--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TELEGRAM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EF0F5F6-A796-4935-9B7D-A39F2D6C2F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECBCD93-0E38-4FD8-97B7-BE8A8D2E3CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5A425CB3-04C0-44CA-B7C2-58517E1F2520}"/>
   </bookViews>
@@ -38,9 +38,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>商品</t>
-  </si>
   <si>
     <t>買進</t>
   </si>
@@ -85,6 +82,9 @@
   </si>
   <si>
     <t>市值</t>
+  </si>
+  <si>
+    <t>stock_id</t>
   </si>
 </sst>
 </file>
@@ -11159,52 +11159,52 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TELEGRAM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECBCD93-0E38-4FD8-97B7-BE8A8D2E3CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43CB1CA0-8FF6-4462-8553-99FC2A98B184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5A425CB3-04C0-44CA-B7C2-58517E1F2520}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{5A425CB3-04C0-44CA-B7C2-58517E1F2520}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>買進</t>
   </si>
@@ -21143,4 +21144,1166 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BAF8EA-464F-4AC6-A4C4-C05D963C28EF}">
+  <dimension ref="A1:A192"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="str">
+        <f t="array" ref="A2">[1]!'6515.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>穎崴</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="str">
+        <f t="array" ref="A3">[1]!'3653.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>健策</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="str">
+        <f t="array" ref="A4">[1]!'7769.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>鴻勁</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="str">
+        <f t="array" ref="A5">[1]!'3529.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>力旺</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="str">
+        <f t="array" ref="A6">[1]!'2059.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>川湖</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="str">
+        <f t="array" ref="A7">[1]!'3081.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>聯亞</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="str">
+        <f t="array" ref="A8">[1]!'7734.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>印能科技</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="str">
+        <f t="array" ref="A9">[1]!'2360.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>致茂</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
+        <f t="array" ref="A10">[1]!'7751.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>竑騰</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="str">
+        <f t="array" ref="A11">[1]!'7750.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>新代</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="str">
+        <f t="array" ref="A12">[1]!'3163.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>波若威</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="str">
+        <f t="array" ref="A13">[1]!'1590.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>亞德客-KY</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="str">
+        <f t="array" ref="A14">[1]!'6187.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>萬潤</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="str">
+        <f t="array" ref="A15">[1]!'2404.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>漢唐</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="str">
+        <f t="array" ref="A16">[1]!'3363.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>上詮</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="str">
+        <f t="array" ref="A17">[1]!'4971.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>IET-KY</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="str">
+        <f t="array" ref="A18">[1]!'3583.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>辛耘</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="str">
+        <f t="array" ref="A19">[1]!'3293.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>鈊象</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="str">
+        <f t="array" ref="A20">[1]!'6139.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>亞翔</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="str">
+        <f t="array" ref="A21">[1]!'4991.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>環宇-KY</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="str">
+        <f t="array" ref="A22">[1]!'4979.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>華星光</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="str">
+        <f t="array" ref="A23">[1]!'6531.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>愛普*</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="str">
+        <f t="array" ref="A24">[1]!'3105.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>穩懋</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="str">
+        <f t="array" ref="A25">[1]!'6643.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>M31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="str">
+        <f t="array" ref="A26">[1]!'6831.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>邁科</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="str">
+        <f t="array" ref="A27">[1]!'6788.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>華景電</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="str">
+        <f t="array" ref="A28">[1]!'5234.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>達興材料</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="str">
+        <f t="array" ref="A29">[1]!'8021.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>尖點</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="str">
+        <f t="array" ref="A30">[1]!'6725.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>矽科宏晟</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="str">
+        <f t="array" ref="A31">[1]!'8358.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>金居</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="str">
+        <f t="array" ref="A32">[1]!'8155.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>博智</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="str">
+        <f t="array" ref="A33">[1]!'5475.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>德宏</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="str">
+        <f t="array" ref="A34">[1]!'6196.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>帆宣</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="str">
+        <f t="array" ref="A35">[1]!'3450.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>聯鈞</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="str">
+        <f t="array" ref="A36">[1]!'3587.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>閎康</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="str">
+        <f t="array" ref="A37">[1]!'6415.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>矽力*-KY</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="str">
+        <f t="array" ref="A38">[1]!'3030.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>德律</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="str">
+        <f t="array" ref="A39">[1]!'2455.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>全新</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="str">
+        <f t="array" ref="A40">[1]!'4958.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>臻鼎-KY</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="str">
+        <f t="array" ref="A41">[1]!'2049.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>上銀</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="str">
+        <f t="array" ref="A42">[1]!'6213.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>聯茂</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="str">
+        <f t="array" ref="A43">[1]!'6217.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>中探針</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="str">
+        <f t="array" ref="A44">[1]!'3555.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>博士旺</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="str">
+        <f t="array" ref="A45">[1]!'6290.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>良維</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="str">
+        <f t="array" ref="A46">[1]!'6426.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>統新</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="str">
+        <f t="array" ref="A47">[1]!'4977.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>眾達-KY</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="str">
+        <f t="array" ref="A48">[1]!'6533.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>晶心科</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="str">
+        <f t="array" ref="A49">[1]!'4764.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>雙鍵</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="str">
+        <f t="array" ref="A50">[1]!'6829.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>千附精密</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="str">
+        <f t="array" ref="A51">[1]!'3455.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>由田</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="str">
+        <f t="array" ref="A52">[1]!'2474.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>可成</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="str">
+        <f t="array" ref="A53">[1]!'3675.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>德微</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="str">
+        <f t="array" ref="A54">[1]!'4576.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>大銀微系統</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="str">
+        <f t="array" ref="A55">[1]!'6933.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>AMAX-KY</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="str">
+        <f t="array" ref="A56">[1]!'3715.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>定穎投控</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="str">
+        <f t="array" ref="A57">[1]!'6197.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>佳必琪</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="str">
+        <f t="array" ref="A58">[1]!'6672.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>騰輝電子-KY</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="str">
+        <f t="array" ref="A59">[1]!'2472.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>立隆電</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="str">
+        <f t="array" ref="A60">[1]!'3357.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>臺慶科</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="str">
+        <f t="array" ref="A61">[1]!'3138.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>耀登</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="str">
+        <f t="array" ref="A62">[1]!'6861.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>睿生光電</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="str">
+        <f t="array" ref="A63">[1]!'6435.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>大中</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="str">
+        <f t="array" ref="A64">[1]!'3042.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>晶技</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="str">
+        <f t="array" ref="A65">[1]!'4755.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>三福化</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="str">
+        <f t="array" ref="A66">[1]!'7788.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>松川精密</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="str">
+        <f t="array" ref="A67">[1]!'6877.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>鏵友益</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="str">
+        <f t="array" ref="A68">[1]!'8147.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>正淩</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="str">
+        <f t="array" ref="A69">[1]!'6278.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>台表科</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="str">
+        <f t="array" ref="A70">[1]!'2597.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>潤弘</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="str">
+        <f t="array" ref="A71">[1]!'1785.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>光洋科</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="str">
+        <f t="array" ref="A72">[1]!'8086.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>宏捷科</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="str">
+        <f t="array" ref="A73">[1]!'6706.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>惠特</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="str">
+        <f t="array" ref="A74">[1]!'4577.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>達航科技</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="str">
+        <f t="array" ref="A75">[1]!'5222.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>全訊</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="str">
+        <f t="array" ref="A76">[1]!'8039.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>台虹</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="str">
+        <f t="array" ref="A77">[1]!'2351.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>順德</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="str">
+        <f t="array" ref="A78">[1]!'3402.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>漢科</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="str">
+        <f t="array" ref="A79">[1]!'7402.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>邑錡</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="str">
+        <f t="array" ref="A80">[1]!'8255.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>朋程</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="str">
+        <f t="array" ref="A81">[1]!'3708.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>上緯投控</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="str">
+        <f t="array" ref="A82">[1]!'6214.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>精誠</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="str">
+        <f t="array" ref="A83">[1]!'8261.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>富鼎</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="str">
+        <f t="array" ref="A84">[1]!'5340.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>建榮</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="str">
+        <f t="array" ref="A85">[1]!'2476.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>鉅祥</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="str">
+        <f t="array" ref="A86">[1]!'6462.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>神盾</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="str">
+        <f t="array" ref="A87">[1]!'1815.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>富喬</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="str">
+        <f t="array" ref="A88">[1]!'3645.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>達邁</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="str">
+        <f t="array" ref="A89">[1]!'3013.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>晟銘電</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="str">
+        <f t="array" ref="A90">[1]!'2481.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>強茂</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="str">
+        <f t="array" ref="A91">[1]!'3388.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>崇越電</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="str">
+        <f t="array" ref="A92">[1]!'6902.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>GOGOLOOK</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="str">
+        <f t="array" ref="A93">[1]!'3430.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>奇鈦科</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="str">
+        <f t="array" ref="A94">[1]!'6425.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>易發</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="str">
+        <f t="array" ref="A95">[1]!'6173.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>信昌電</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="str">
+        <f t="array" ref="A96">[1]!'8438.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>昶昕</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="str">
+        <f t="array" ref="A97">[1]!'2464.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>盟立</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="str">
+        <f t="array" ref="A98">[1]!'6532.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>瑞耘</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="str">
+        <f t="array" ref="A99">[1]!'6245.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>立端</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="str">
+        <f t="array" ref="A100">[1]!'6456.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>GIS-KY</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="str">
+        <f t="array" ref="A101">[1]!'6823.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>濾能</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="str">
+        <f t="array" ref="A102">[1]!'6735.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>美達科技</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="str">
+        <f t="array" ref="A103">[1]!'6205.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>詮欣</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="str">
+        <f t="array" ref="A104">[1]!'1717.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>長興</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="str">
+        <f t="array" ref="A105">[1]!'6166.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>凌華</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="str">
+        <f t="array" ref="A106">[1]!'8111.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>立碁</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="str">
+        <f t="array" ref="A107">[1]!'2402.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>毅嘉</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="str">
+        <f t="array" ref="A108">[1]!'2303.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>聯電</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="str">
+        <f t="array" ref="A109">[1]!'2478.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>大毅</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="str">
+        <f t="array" ref="A110">[1]!'3055.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>蔚華科</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="str">
+        <f t="array" ref="A111">[1]!'3054.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>立萬利</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="str">
+        <f t="array" ref="A112">[1]!'6994.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>富威電力</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="str">
+        <f t="array" ref="A113">[1]!'3504.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>揚明光</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="str">
+        <f t="array" ref="A114">[1]!'3673.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>TPK-KY</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="str">
+        <f t="array" ref="A115">[1]!'8048.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>德勝</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="str">
+        <f t="array" ref="A116">[1]!'1802.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>台玻</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="str">
+        <f t="array" ref="A117">[1]!'3709.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>鑫聯大投控</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="str">
+        <f t="array" ref="A118">[1]!'6821.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>聯寶</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="str">
+        <f t="array" ref="A119">[1]!'8383.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>千附</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="str">
+        <f t="array" ref="A120">[1]!'3701.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>大眾控</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="str">
+        <f t="array" ref="A121">[1]!'6909.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>創控</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="str">
+        <f t="array" ref="A122">[1]!'3339.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>泰谷</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" t="str">
+        <f t="array" ref="A123">[1]!'2388.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>威盛</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" t="str">
+        <f t="array" ref="A124">[1]!'5425.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>台半</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" t="str">
+        <f t="array" ref="A125">[1]!'6224.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>聚鼎</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" t="str">
+        <f t="array" ref="A126">[1]!'4540.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>全球傳動</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" t="str">
+        <f t="array" ref="A127">[1]!'3707.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>漢磊</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" t="str">
+        <f t="array" ref="A128">[1]!'6548.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>長科*</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" t="str">
+        <f t="array" ref="A129">[1]!'2363.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>矽統</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" t="str">
+        <f t="array" ref="A130">[1]!'4956.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>光鋐</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" t="str">
+        <f t="array" ref="A131">[1]!'8289.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>泰藝</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" t="str">
+        <f t="array" ref="A132">[1]!'3317.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>尼克森</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" t="str">
+        <f t="array" ref="A133">[1]!'6465.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>威潤</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" t="str">
+        <f t="array" ref="A134">[1]!'1711.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>永光</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" t="str">
+        <f t="array" ref="A135">[1]!'4927.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>泰鼎-KY</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" t="str">
+        <f t="array" ref="A136">[1]!'3594.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>磐儀</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" t="str">
+        <f t="array" ref="A137">[1]!'5244.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>弘凱</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" t="str">
+        <f t="array" ref="A138">[1]!'3545.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>敦泰</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" t="str">
+        <f t="array" ref="A139">[1]!'2070.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>精湛</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" t="str">
+        <f t="array" ref="A140">[1]!'8088.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>品安</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" t="str">
+        <f t="array" ref="A141">[1]!'2338.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>光罩</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" t="str">
+        <f t="array" ref="A142">[1]!'8070.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>長華*</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" t="str">
+        <f t="array" ref="A143">[1]!'2484.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>希華</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" t="str">
+        <f t="array" ref="A144">[1]!'6432.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>今展科</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" t="str">
+        <f t="array" ref="A145">[1]!'8942.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>森鉅</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" t="str">
+        <f t="array" ref="A146">[1]!'8182.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>加高</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" t="str">
+        <f t="array" ref="A147">[1]!'3230.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>錦明</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" t="str">
+        <f t="array" ref="A148">[1]!'8104.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>錸寶</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" t="str">
+        <f t="array" ref="A149">[1]!'4960.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>誠美材</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" t="str">
+        <f t="array" ref="A150">[1]!'8183.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>精星</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" t="str">
+        <f t="array" ref="A151">[1]!'5228.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>鈺鎧</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" t="str">
+        <f t="array" ref="A152">[1]!'3615.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>安可</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" t="str">
+        <f t="array" ref="A153">[1]!'2365.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>昆盈</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" t="str">
+        <f t="array" ref="A154">[1]!'3685.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>元創精密</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" t="str">
+        <f t="array" ref="A155">[1]!'3092.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>鴻碩</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" t="str">
+        <f t="array" ref="A156">[1]!'6141.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>柏承</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" t="str">
+        <f t="array" ref="A157">[1]!'4556.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>旭然</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" t="str">
+        <f t="array" ref="A158">[1]!'6174.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>安碁</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" t="str">
+        <f t="array" ref="A159">[1]!'3437.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>榮創</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" t="str">
+        <f t="array" ref="A160">[1]!'6168.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>宏齊</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" t="str">
+        <f t="array" ref="A161">[1]!'3518.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>柏騰</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" t="str">
+        <f t="array" ref="A162">[1]!'1442.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>名軒</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" t="str">
+        <f t="array" ref="A163">[1]!'8121.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>越峰</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" t="str">
+        <f t="array" ref="A164">[1]!'3591.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>艾笛森</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" t="str">
+        <f t="array" ref="A165">[1]!'8215.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>明基材</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" t="str">
+        <f t="array" ref="A166">[1]!'6603.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>富強鑫</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" t="str">
+        <f t="array" ref="A167">[1]!'4720.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>德淵</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" t="str">
+        <f t="array" ref="A168">[1]!'2401.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>凌陽</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" t="str">
+        <f t="array" ref="A169">[1]!'8068.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>全達</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" t="str">
+        <f t="array" ref="A170">[1]!'2462.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>良得電</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" t="str">
+        <f t="array" ref="A171">[1]!'1721.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>三晃</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" t="str">
+        <f t="array" ref="A172">[1]!'3550.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>聯穎</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" t="str">
+        <f t="array" ref="A173">[1]!'3712.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>永崴投控</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" t="str">
+        <f t="array" ref="A174">[1]!'3511.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>矽瑪</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" t="str">
+        <f t="array" ref="A175">[1]!'4564.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>元翎</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" t="str">
+        <f t="array" ref="A176">[1]!'8059.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>凱碩</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" t="str">
+        <f t="array" ref="A177">[1]!'2302.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>麗正</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" t="str">
+        <f t="array" ref="A178">[1]!'6153.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>嘉聯益</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" t="str">
+        <f t="array" ref="A179">[1]!'2705.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>六福</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" t="str">
+        <f t="array" ref="A180">[1]!'4934.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>太極</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" t="str">
+        <f t="array" ref="A181">[1]!'2491.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>吉祥全</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" t="str">
+        <f t="array" ref="A182">[1]!'2702.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>華園</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" t="str">
+        <f t="array" ref="A183">[1]!'6226.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>光鼎</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" t="str">
+        <f t="array" ref="A184">[1]!'4707.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>磐亞</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" t="str">
+        <f t="array" ref="A185">[1]!'4416.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>三圓</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" t="str">
+        <f t="array" ref="A186">[1]!'4716.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>大立</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" t="str">
+        <f t="array" ref="A187">[1]!'3607.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>谷崧</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" t="str">
+        <f t="array" ref="A188">[1]!'2444.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>兆勁</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" t="str">
+        <f t="array" ref="A189">[1]!'3011.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>今皓</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" t="str">
+        <f t="array" ref="A190">[1]!'3024.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>憶聲</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" t="str">
+        <f t="array" ref="A191">[1]!'1626.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>艾美特-KY</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" t="str">
+        <f t="array" ref="A192">[1]!'1455.TW-Name,Bid,Ask,Price,PriceChange,PriceChangeRatio,Volume,TotalVolume,BestBidSize,BestAskSize'</f>
+        <v>集盛</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>